--- a/shackles/shackle-data.xlsx
+++ b/shackles/shackle-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\Automation\certificate\shackles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC1BD73-22DF-42F4-A055-A457CB57B926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001ADFA6-F2C4-46E8-B744-61C98EB96B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" xr2:uid="{0BF442CD-8932-45B5-8865-ED7FBD54BAD9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0BF442CD-8932-45B5-8865-ED7FBD54BAD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
